--- a/business_forms/043_facility_and_production_capabilities_survey--business_forms.xlsx
+++ b/business_forms/043_facility_and_production_capabilities_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>production_capacity</t>
+          <t>facility_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Production Capacity</t>
+          <t>Facility Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>production_capacity_1</t>
+          <t>production_capacity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Production Capacity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>facility_type</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Facility Type</t>
+          <t>Contact Info</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>contact_info2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Contact Info 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Facility Location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,338 +750,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>facility_info_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Facility Info 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>contact_person</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Contact Person</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>facility_location</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Facility Location</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>production_capacity_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Production Capacity</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>production_capacity_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Production Capacity</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>production_capacity_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Production Capacity</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>production_capacity_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Production Capacity</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>facility_info_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Facility Info</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>facility_info_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Facility Info</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>facility_info_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Facility Info</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>facility_info_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Facility Info</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>facility_info_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Facility Info</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>facility_info_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Facility Info</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +779,9 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manufacturing_facility'}</t>
+          <t>manufacturing_facility</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manufacturing Facility'}</t>
+          <t>Manufacturing Facility</t>
         </is>
       </c>
     </row>
@@ -1148,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service_facility'}</t>
+          <t>service_facility</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Service Facility'}</t>
+          <t>Service Facility</t>
         </is>
       </c>
     </row>
@@ -1165,97 +843,97 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>facility_location_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'north_america'}</t>
+          <t>north_america</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'North America'}</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>facility_location_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'south_america'}</t>
+          <t>south_america</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'South America'}</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>facility_location_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>facility_location_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'asia'}</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Asia'}</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>facility_location_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'africa'}</t>
+          <t>africa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Africa'}</t>
+          <t>Africa</t>
         </is>
       </c>
     </row>
